--- a/funding-agent/data/oportunidades_atraccion_recursos_vision_circular.xlsx
+++ b/funding-agent/data/oportunidades_atraccion_recursos_vision_circular.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI51"/>
+  <dimension ref="A1:AI75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -9438,6 +9438,4254 @@
         </is>
       </c>
       <c r="AI51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VC-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Incentivo al Aprovechamiento y Tratamiento de Residuos Sólidos, IAT 2026 – Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Alcaldía de Dosquebradas</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Colombia (Dosquebradas, Risaralda)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Residuos y reciclaje</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Inclusión de recicladores, Aprovechamiento y tratamiento de residuos</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Fortalecimiento institucional; Inclusión social</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Más de 1.400 millones</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://www.dosquebradas.gov.co/web/index.php/dosquebradas/ciudad/sala-de-prensa/noticias/303-vigencia-2026/9546-dosquebradas-abre-convocatoria-por-mas-de-1-400-millones-para-transformar-el-manejo-de-residuos-en-el-municipio</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>La Alcaldía de Dosquebradas abrió convocatoria para financiar proyectos de aprovechamiento y tratamiento de residuos sólidos con más de $1.400 millones COP. Las organizaciones de recicladores en proceso de formalización y prestadores del servicio de aseo pueden postular proyectos hasta el 30 de julio de 2026. Busca fortalecer capacidad operativa del sector y avanzar hacia un modelo de ciudad sostenible.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Altamente relevante porque apoya la inclusión y formalización de recicladores de oficio, pilar clave de Visión Circular. Financia proyectos de aprovechamiento y tratamiento de residuos, en línea con cierre de ciclo, economía circular territorial y cumplimiento de normativa REP.</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de organizaciones de recicladores; Proyectos piloto de aprovechamiento de residuos posconsumo; Implementación de infraestructura para separación y tratamiento; Modelos de economía circular municipal; Capacitación y formalización de recicladores.</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ser organización de recicladores en proceso de formalización o prestador del servicio público de aseo; Presentar proyecto orientado a aprovechamiento/tratamiento de residuos; Operar o tener interés en Dosquebradas</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Propuesta de proyecto; Documentación legal de la organización; Plan técnico y operativo; Presupuesto detallado (inferido de convocatorias similares)</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Organizaciones de recicladores de Dosquebradas; Acoplásticos; Cámara de Comercio de Dosquebradas; ANDI Visión Circular; Empresas locales generadoras de residuos; Universidades regionales</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Elegibilidad restringida a Dosquebradas; Puede exigir formalización previa de organizaciones; Posible competencia alta por recursos limitados municipales</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Contactar organizaciones de recicladores en Dosquebradas para explorar alianzas y cofinanciación de proyectos piloto que puedan escalarse. Revisar términos de referencia completos en alcaldía.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Solicitar términos completos de convocatoria a la Alcaldía de Dosquebradas; Identificar organizaciones de recicladores y prestadores de aseo elegibles; Evaluar viabilidad de cofinanciar proyecto piloto desde Visión Circular</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos territoriales / Alianzas con recicladores</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Convocatoria municipal con alta alineación temática. La elegibilidad parece restringida a actores locales de Dosquebradas, pero Visión Circular podría articularse como cofinanciador o socio técnico. Fecha de cierre confirmada (30 julio 2026). Monto en COP sin desglose por proyecto. | Fuente fuera del listado oficial conocido (dosquebradas.gov.co): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>0c5a3e4a94ccd561</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VC-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Google.org AI for Science and Society</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Google.org</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Global (incluye Colombia y América Latina)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Innovación tecnológica</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial aplicada a problemas sociales y científicos</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Asistencia técnica; Innovación</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No especificado (fondos globales)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>https://www.asocapitales.co/sites/default/files/files/technical_documents/boletin-cooperacion-internacional-marzo-2026-2.pdf</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Google.org abre convocatoria para financiar proyectos que utilicen inteligencia artificial para resolver problemas científicos y sociales. Dirigida a universidades, ONGs y entidades estatales con áreas de innovación. Ofrece fondos globales y acompañamiento de expertos de Google. Fecha límite 17 de abril de 2026.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Oportunidad para proyectos de IA aplicada a economía circular: clasificación automatizada de residuos, pasaportes digitales de productos (como el piloto mencionado en ANDI), optimización de cadenas de reciclaje, trazabilidad de materiales, visión artificial para identificación de plásticos, modelos predictivos de generación de residuos.</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pasaporte digital de productos con IA y visión artificial (como piloto ANDI 2025); Clasificación inteligente de residuos con IA; Plataformas de trazabilidad de empaques; Modelos predictivos para optimización de rutas de recolección; Herramientas de diagnóstico de reciclabilidad de materiales.</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ser universidad, ONG o entidad estatal con área de innovación; Proyecto aplicado a problemas científicos o sociales usando IA; Capacidad técnica demostrable</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Universidades con programas de IA (Uniandes, Javeriana, Nacional); Centros de investigación tecnológica; Acoplásticos; Cámara de Comercio de Bogotá; Empresas transformadoras de plásticos; Organizaciones de recicladores tecnificadas</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Requiere capacidad técnica alta en IA; Competencia global; Términos y URL oficial no disponibles en la fuente; Puede priorizarse impacto social de gran escala sobre proyectos locales</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Buscar convocatoria oficial en Google.org antes del 17 de abril. Explorar alianza con universidades o centros tecnológicos para presentar proyecto de IA aplicada a economía circular de plásticos (ej. pasaporte digital, clasificación inteligente).</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Visitar Google.org y buscar convocatoria vigente; Contactar universidades aliadas para evaluar capacidad técnica; Definir caso de uso de IA prioritario para Visión Circular (sugerencia: pasaporte digital de productos)</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Coordinación de innovación / Alianzas con universidades</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Alta pertinencia por potencial aplicación de IA a economía circular y trazabilidad de materiales. Probabilidad media por requerimientos técnicos y competencia global. Requiere verificación de URL oficial, términos y elegibilidad específica. Fecha de cierre próxima (17 abril 2026). | Fuente fuera del listado oficial conocido (asocapitales.co): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>257b4b99f24027a5</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VC-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Programa de innovación para la circularidad de los plásticos en América Latina 2025 – WRAP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WRAP (Waste and Resources Action Programme) / Red Global de Pactos por los Plásticos / Pacto por los Plásticos Colombia, México y Chile</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Reino Unido / Red Global</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Colombia, México, Chile</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Economía circular de plásticos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Plásticos flexibles, Gestión de residuos plásticos, Innovación en reciclaje</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Aceleración; Asistencia técnica; Piloto demostrativo; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Hasta USD 10.000 por solución (hasta 10 soluciones)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Noviembre 2025 (inferido)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>No especificado (convocatoria 2025, vigente a fecha del reporte)</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://wrap.org.uk/taking-action/plastic-packaging/global-plastics-pact-network/innovation-programme-latin-america-2025</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>https://www.pactoglobal-colombia.org/news/convocatoria-regional-otorgara-hasta-usd-10-000-a-soluciones-innovadoras-en-plasticos-en-colombia-chile-y-mexico.html</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>WRAP y la Red Global de Pactos por los Plásticos ofrecen hasta USD 10.000 por solución (10 soluciones totales) a iniciativas empresariales innovadoras en Colombia, Chile y México que prevengan contaminación por plásticos, con foco en plásticos flexibles (sachets, multilaminados, bolsas, etiquetas). Incluye talleres especializados, acceso a red empresarial global, conexión con inversionistas, pilotos personalizados y fortalecimiento para escalabilidad.</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Altamente relevante porque aborda plásticos flexibles, uno de los mayores retos de Visión Circular y REP en Colombia. Apoya innovación en reciclaje, modelos de negocio circulares y conexión con empresas y financiadores. Alineado con cierre de ciclo de empaques y ecodiseño.</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Tecnologías de reciclaje de plásticos flexibles multicapa; Modelos de recolección y clasificación de sachets y multilaminados; Soluciones de ecodiseño para empaques flexibles; Pilotos de aprovechamiento de etiquetas y bolsas; Innovaciones en reciclaje químico de flexibles; Plataformas de trazabilidad de plásticos.</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ser iniciativa empresarial o emprendimiento con solución innovadora en gestión de plásticos; Foco en plásticos flexibles; Operar o tener interés en Colombia, México o Chile; Capacidad de escalamiento</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Formulario de aplicación disponible en sitio de WRAP; Descripción de la solución innovadora; Modelo de negocio; Capacidad técnica y comercial (inferido)</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Pacto por los Plásticos Colombia; Acoplásticos; Empresas transformadoras de flexibles; Cempre Colombia; Universidades con investigación en materiales; Inversionistas de impacto; Red Global de Pactos por los Plásticos</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Monto limitado (USD 10.000 por solución); Alta competencia regional (3 países); Puede priorizarse innovaciones con mayor potencial de escalamiento rápido; Fecha de cierre no especificada en fuentes disponibles</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Difundir convocatoria entre empresas, emprendedores y aliados del ecosistema de Visión Circular con soluciones en plásticos flexibles. Apoyar formulación de propuestas que integren ecodiseño, reciclabilidad y modelos de negocio circulares. Conectar con Pacto por los Plásticos Colombia para orientación.</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Visitar URL oficial de WRAP para revisar términos completos y fecha de cierre; Identificar empresas y emprendimientos del portafolio de Visión Circular elegibles; Organizar sesión informativa con Pacto por los Plásticos Colombia</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Coordinación de innovación / Alianzas empresariales</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Convocatoria altamente pertinente y con elegibilidad clara para Colombia. Monto relativamente bajo pero con alto valor en asistencia técnica, red de contactos y visibilidad. Fecha de cierre no especificada en las fuentes, requiere confirmación urgente en sitio oficial de WRAP. | Fuente fuera del listado oficial conocido (wrap.org.uk): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>ff66bee202662b3d</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VC-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Convocatoria Origination Facility 2025 – Fondo Neerlandés para el Clima y el Desarrollo (DFCD)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Dutch Fund for Climate and Development (DFCD) / Gobierno de los Países Bajos</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Fondo climático</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Países Bajos</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Global (incluye Colombia, con acompañamiento de BankPro Bogotá)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Financiamiento climático</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Proyectos climáticos en fase temprana, Mitigación y adaptación</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Financiamiento climático; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Hasta 350.000 EUR por proyecto</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Abierta todo 2025, meta interna 30 noviembre 2025 (BankPro Bogotá)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>https://www.pactoglobal-colombia.org/news/convocatoria-internacional-impulsa-proyectos-de-sostenibilidad-en-bogota-region-con-apoyo-de-pacto-global-red-colombia-y-la-agencia-atenea.html</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>El Fondo Neerlandés para el Clima y el Desarrollo otorga hasta 350.000 EUR en subvención para estructuración de proyectos climáticos en fase temprana, reduciendo riesgos iniciales y fortaleciendo base técnica y financiera para acceder a inversiones de mayor escala. Convocatoria abierta en 2025, con acompañamiento de BankPro Bogotá (ATENEA) para empresas colombianas. Meta interna de postulación: 30 noviembre 2025.</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Relevante para estructurar proyectos de economía circular con impacto climático en fase temprana: reducción de emisiones GEI por reciclaje, sustitución de vírgenes por reciclados, infraestructura de aprovechamiento, modelos de negocio circulares. El monto permite financiar estudios de viabilidad, diseño técnico, análisis de mercado y estructuración financiera de proyectos grandes.</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Estructuración de plantas de reciclaje o transformación con impacto climático; Modelos de economía circular territorial con reducción de emisiones; Proyectos de aprovechamiento energético de residuos; Estudios de viabilidad para reciclaje químico o avanzado; Infraestructura de acopio y logística inversa con impacto climático medible.</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Proyecto climático en fase temprana (mitigación o adaptación); Necesidad de estructuración técnica y financiera; Potencial de acceder a inversión de mayor escala posteriormente; Capacidad de articulación con BankPro Bogotá (para empresas de Bogotá-Región)</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>No especificado (inferido: concepto de proyecto, análisis preliminar de impacto climático, plan de estructuración, proyección de inversión futura)</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>ATENEA Bogotá / BankPro; Pacto Global Red Colombia; Empresas con proyectos climáticos; Consultoras especializadas en estructuración de proyectos; Fondos de inversión climática; ANDI; Acoplásticos; Universidades</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Proceso de estructuración puede ser largo y complejo; Requiere proyectos con potencial de escalamiento a inversión mayor; Puede priorizar proyectos de mitigación climática con alto impacto medible; Acompañamiento de BankPro Bogotá puede favorecer proyectos de Bogotá-Región</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Contactar BankPro (ATENEA) para recibir acompañamiento en preparación de propuesta. Identificar proyectos de Visión Circular en fase de concepto o piloto con potencial de escalamiento que requieran estructuración técnica y financiera. Priorizar proyectos con impacto climático cuantificable.</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Contactar ATENEA Bogotá / BankPro para sesión de diagnóstico; Buscar convocatoria oficial del DFCD; Identificar proyectos elegibles del portafolio de Visión Circular; Evaluar asistencia de consultor para estructuración de propuesta antes del 30 noviembre</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Dirección de programa / Coordinación de financiamiento climático</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Oportunidad de alto valor (hasta 350.000 EUR) para estructuración de proyectos en fase temprana. Requiere capacidad técnica de preparación de propuestas climáticas. BankPro Bogotá ofrece acompañamiento metodológico, lo que aumenta probabilidad de éxito. Meta interna 30 noviembre 2025 permite planificación. URL oficial y términos completos deben buscarse en sitio del DFCD. | Fuente fuera del listado oficial conocido (pactoglobal-colombia.org): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>3acf2df9f66fdce9</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VC-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Convocatoria LATAM 2025: Innovación para la Circularidad de Plásticos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>WRAP y Red Global de Pactos de los Plásticos</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Reino Unido / Global</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>México, Colombia y Chile</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Plásticos flexibles</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Premio o challenge; Innovación</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DOEdOa2jgcI</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Premio regional que busca las 10 soluciones más prometedoras de México, Colombia y Chile para mejorar el sistema de plásticos flexibles. Enfocado en tres desafíos: reducción de plásticos problemáticos, habilitación del reciclaje mediante innovación en diseño/tecnología, y creación de mercados finales para materiales reciclados (polipropileno, poliolefinas mixtas). Lanzado por WRAP y la Red Global de Pactos de los Plásticos.</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Altamente pertinente. El desafío de plásticos flexibles es prioritario para Visión Circular ANDI, dada la complejidad de reciclaje de este material. La convocatoria aborda ecodiseño, reciclabilidad y creación de mercados secundarios, tres pilares centrales del programa.</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Innovación en ecodiseño de empaques flexibles mono-material; Tecnologías de separación y reciclaje de multicapa; Desarrollo de mercados finales para poliolefinas recicladas; Modelos de negocio para circularidad de sachets y envoltorios; Pilotos empresariales de sustitución de flexibles problemáticos.</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Soluciones innovadoras que aborden al menos uno de los tres desafíos clave; Aplicabilidad en México, Colombia o Chile; Potencial de mejora del sistema de plásticos flexibles.</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Empresas de envases y empaques flexible (Carvajal, Alico, Alpla), Pacto por los Plásticos Colombia, universidades con investigación en polímeros (EAFIT, Nacional), centros de innovación (ICIPC), recicladores especializados.</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>No se especifica el monto del premio ni las fechas exactas de cierre; Posiblemente ya cerrada si el post es antiguo; Competencia regional con México y Chile.</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Verificar urgentemente vigencia de la convocatoria contactando a WRAP o Pacto por los Plásticos Colombia; Si está abierta, convocar a empresas del programa Visión Circular con innovaciones en flexibles para postulación conjunta.</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Contactar a WRAP Latinoamérica y Pacto por los Plásticos Colombia para confirmar fechas y términos; Solicitar bases oficiales; Mapear proyectos elegibles en portafolio Visión Circular.</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Coordinación técnica de Visión Circular / Especialista en plásticos flexibles</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>El post de Instagram no especifica fechas ni enlace oficial a bases. Se infiere que es convocatoria 2025 pero no hay confirmación de vigencia actual. La fuente es una publicación en redes sociales, por lo que requiere validación urgente con WRAP o el Pacto por los Plásticos. | Fuente fuera del listado oficial conocido (instagram.com): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>cf8871d36ac1d130</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VC-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Convocatoria EcoCiclo - Ecodiseño y Sustitución de Plásticos de Un Solo Uso</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Agencia ATENEA (Agencia Distrital para la Educación Superior, la Ciencia y la Tecnología de Bogotá)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bogotá, Colombia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ecodiseño; Envases y empaques</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Cofinanciación; Investigación aplicada; Innovación</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Sí, requiere alianza estratégica entre centros de investigación y empresas</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://agenciaatenea.gov.co/noticias/agencia-atenea-lanza-convocatoria-para-promover-la-sustitucion-de-plasticos-de-un-solo-uso-y-el</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Primera convocatoria distrital en economía circular enfocada en reducción de impacto ambiental. Busca conformar un Banco de Proyectos de investigación e innovación mediante alianzas estratégicas entre centros de investigación y empresas usuarias de empaques/envases. Temáticas: aprovechamiento de residuos de empaques/envases, fomento de soluciones sostenibles y promoción de prácticas responsables hacia economía circular. Cierra el 25 de septiembre de 2025. Los proyectos se conocerán el 3 de noviembre de 2025.</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Altamente relevante para Visión Circular. Aborda ecodiseño de envases/empaques y sustitución de plásticos de un solo uso, dos líneas estratégicas centrales. La articulación universidad-empresa-gremio es un modelo replicable para ANDI a nivel nacional.</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ecodiseño de envases para reducir impacto ambiental; Tecnologías de aprovechamiento de residuos post-consumo de empaques; Sustitución de plásticos de un solo uso por alternativas circulares; Investigación en materiales de fuentes secundarias; Pilotos de circularidad en empresas de consumo masivo.</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alianza estratégica entre centros de investigación/universidades y empresas que utilicen empaques y envases; Proyecto de investigación, innovación o desarrollo tecnológico; Enfoque en ecodiseño o sustitución de plásticos de un solo uso o aprovechamiento de residuos.</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Términos de referencia completos (disponibles en la URL oficial)</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Universidades de Bogotá (Nacional, Andes, Javeriana, EAN), empresas miembro de ANDI del sector alimentos/bebidas/cuidado personal, CEMPRE Colombia, Pacto por los Plásticos, laboratorios de materiales (ICIPC).</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Limitado a Bogotá (puede excluir empresas nacionales sin presencia en la ciudad); Requiere capacidad de investigación aplicada y contrapartida empresarial; Plazos ajustados para formular proyectos complejos.</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Revisar términos de referencia completos; Convocar a empresas miembro de Visión Circular con operaciones en Bogotá; Mapear aliados académicos disponibles; Priorizar proyectos en envases flexibles o plásticos de un solo uso con alto impacto.</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Descargar y analizar términos de referencia completos de la convocatoria; Socializar oportunidad en próxima reunión de Visión Circular; Identificar empresas y centros de investigación para alianzas antes del 15 de septiembre.</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Coordinación de innovación y desarrollo tecnológico de Visión Circular / Enlace con universidades</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Convocatoria confirmada y vigente hasta septiembre 2025. Fecha de publicación de proyectos financiables es clara (3 de noviembre). Sin embargo, el monto total disponible no se especifica en la fuente. Requiere verificación de términos completos para confirmar montos y contrapartidas. | Fuente fuera del listado oficial conocido (agenciaatenea.gov.co): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>e585d33022b89de1</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VC-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fondo para la Vida y la Biodiversidad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente y Desarrollo Sostenible de Colombia</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ambiente y biodiversidad</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Economía baja en carbono; Adaptación climática; Capital natural</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Financiamiento concesional; Donación; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Más de $5 billones COP proyectados al 2026</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://www.minambiente.gov.co/fondo-para-la-vida</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Instrumento financiero nacional para transitar hacia economía baja en carbono, promover adaptación climática, proteger capital natural y beneficiar poblaciones vulnerables. Administrado por sociedad fiduciaria. Los proyectos son definidos por el Consejo Directivo según prioridades. Se proyectan más de $5 billones COP en inversión al 2026 en proyectos ambientales.</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Pertinencia indirecta pero relevante. Aunque no se enfoca específicamente en economía circular de envases/empaques, el fondo financia transición a economía baja en carbono que incluye aprovechamiento de residuos, reducción de emisiones en ciclos productivos y beneficio a poblaciones vulnerables (recicladores). Puede financiar componentes de infraestructura REP o modelos circulares territoriales.</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Infraestructura de aprovechamiento de residuos con reducción de emisiones; Proyectos de inclusión de recicladores con enfoque de adaptación; Modelos circulares territoriales en economía baja en carbono; Proyectos demostrativos de cierre de ciclo con co-beneficios climáticos.</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Proyectos priorizados por el Consejo Directivo del Fondo; Alineación con objetivos de economía baja en carbono, adaptación climática, protección de capital natural o beneficio a poblaciones vulnerables.</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente, Parques Nacionales, autoridades ambientales regionales, empresas con compromisos climáticos (miembro de ANDI), organizaciones de recicladores, universidades.</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Criterios de priorización no son públicos; Decisión centralizada en Consejo Directivo; No hay convocatoria abierta para postulación directa; Puede requerir articulación política o institucional previa.</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con Minambiente para conocer mecanismos de priorización de proyectos; Evaluar alineación de proyectos actuales de Visión Circular con objetivos del Fondo; Preparar propuestas con co-beneficios climáticos y sociales para presentar ante Consejo Directivo.</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Contactar a la Dirección de Asuntos Ambientales de Minambiente para entender proceso de priorización; Mapear proyectos elegibles en portafolio Visión Circular con enfoque climático.</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Dirección de relaciones institucionales de ANDI / Coordinación de alianzas estratégicas</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>El Fondo existe y está operando, pero no tiene convocatoria pública abierta ni términos de postulación directa. Los proyectos son priorizados por el Consejo Directivo. Esto limita la probabilidad de acceso directo, pero no la descarta si se articula institucionalmente. La pertinencia es indirecta pero existe espacio para proyectos circulares con componente climático.</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>47188e11947c92a2</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VC-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Programa Empleos Verdes de la Economía Circular (PREVEC) - Cooperación Colombia-Alemania</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GIZ Alemania y Gobierno de Colombia (Minambiente, SENA)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cooperación bilateral</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Inclusión de recicladores; Empleos verdes; Capacitación</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Cooperación técnica; Asistencia técnica; Fortalecimiento institucional; Inclusión social</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No especificado; incluye apoyo económico a asociaciones de recicladores (mencionado por Minambiente)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://www.minambiente.gov.co/gobierno-plantea-apoyo-economico-para-fortalecer-asociaciones-de-recicladores</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Proyecto de cooperación bilateral Colombia-Alemania que articula sectores público, privado, población recicladora y cooperación internacional para fortalecer la ruta hacia economía circular que priorice vida y medio ambiente. Incluye certificación de 2.000 recicladores/año en el Laboratorio de Economía Circular del SENA (construido con apoyo GIZ). La ministra Muhamad anunció apoyo económico para formalización de asociaciones de recicladores, maquinaria y crédito.</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Altamente relevante. PREVEC articula exactamente los actores que Visión Circular convoca: sector público, privado, recicladores y cooperación. El componente de certificación y fortalecimiento de asociaciones es clave para la inclusión efectiva en REP y cadenas circulares.</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de asociaciones de recicladores con acceso a maquinaria y crédito; Certificación de competencias laborales en reciclaje y economía circular; Proyectos piloto empresa-recicladores con enfoque de empleos verdes; Innovación en modelos de reciclaje inclusivo con transferencia tecnológica alemana.</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Asociaciones de recicladores formalizadas o en proceso; Empresas comprometidas con inclusión y economía circular; Alineación con objetivos de empleos verdes y economía popular.</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>GIZ Colombia, SENA, Minambiente, Asociación Nacional de Recicladores, cooperativas regionales (ej. Cooperchacol), empresas miembro ANDI con programas REP, universidades.</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>No hay convocatoria pública abierta; Los recursos y criterios de acceso al apoyo económico no están detallados; Requiere articulación directa con GIZ y Minambiente.</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con GIZ Colombia y Minambiente para conocer mecanismos de acceso a PREVEC; Proponer pilotos Visión Circular-PREVEC en territorios estratégicos; Articular certificación SENA con empresas miembro.</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Contactar a GIZ Colombia (Embajada Alemana) y Dirección de Economía Circular de Minambiente; Mapear asociaciones de recicladores en territorios prioritarios de Visión Circular.</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Coordinación de cooperación internacional y alianzas de ANDI / Visión Circular</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Es un programa activo de cooperación bilateral, no una convocatoria abierta. El acceso requiere articulación institucional directa. La ministra Muhamad confirmó apoyo económico a recicladores pero no se detallan montos, mecanismos ni cronograma. Requiere verificación de instrumentos específicos disponibles.</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>e19b15c776c36167</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VC-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Plan de Respuesta de Asistencia Técnica en Economía Circular - CTCN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Climate Technology Centre and Network (CTCN)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Agencia ONU</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ecuador, Costa Rica, República Dominicana, Colombia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Desarrollo de Hojas de Ruta de Economía Circular, cooperación sur-sur, plataforma regional</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Asistencia técnica; Cooperación técnica; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://www.ctc-n.org/system/files/response_plans/plan_de_respuesta_economia_circular_ii_final.pdf</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>El CTCN está ejecutando un plan de asistencia técnica para economía circular en cuatro países de América Latina (Ecuador, Costa Rica, República Dominicana y Colombia). Incluye reuniones nacionales, talleres regionales, creación de hojas de ruta, identificación de actores clave, estudios de caso y una plataforma regional de cooperación sur-sur. Énfasis en igualdad de género (ODS 5).</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Altamente relevante para Visión Circular ANDI: asistencia técnica regional en economía circular, desarrollo de hojas de ruta nacionales, identificación de actores clave, y plataforma de cooperación sur-sur que puede fortalecer capacidades institucionales y proyectos en Colombia.</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Participación en talleres regionales; co-creación de hoja de ruta de economía circular Colombia; intercambio de casos de estudio (envases, empaques, reciclaje); integración a plataforma regional; cooperación sur-sur con países vecinos</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Participación de actores clave nacionales con experiencia y capacidades en economía circular; compromiso institucional; enfoque de género</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente y Desarrollo Sostenible, ANDI, gremios empresariales, universidades, centros tecnológicos, organizaciones de recicladores</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Documento es un plan de respuesta sin fechas claras de ejecución; no se especifica si el programa está abierto a nuevos participantes o si Colombia ya está incluida</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Verificar con CTCN el estado actual del plan de asistencia técnica y si Colombia (ANDI) puede sumarse oficialmente como actor clave; explorar participación en talleres y plataforma regional</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Contactar oficina CTCN Colombia o punto focal nacional para confirmar vigencia, fechas de talleres y mecanismo de vinculación formal de ANDI/Visión Circular</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos internacionales / Alianzas estratégicas</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>El documento es un plan de respuesta técnico que menciona reuniones en Colombia y otros países, pero no especifica fechas exactas ni estado actual de ejecución. La asistencia técnica parece estar en curso o próxima a ejecutarse, pero requiere confirmación oficial. | Fuente fuera del listado oficial conocido (ctc-n.org): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>1e667076cb038921</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VC-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ProUSAR - Fomentar la economía circular en Colombia mediante la innovación</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Deutsche Gesellschaft für Internationale Zusammenarbeit (GIZ)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Cooperación bilateral</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ecodiseño, producción upstream, envases y empaques, textil, electrónicos, reciclabilidad</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Cooperación técnica; Asistencia técnica; Innovación; Piloto demostrativo</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>6.800.000</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Proyecto vigente - actualizado febrero 2025</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://www.giz.de/en/projects/fomentar-la-economia-circular-en-colombia-mediante-la-innovacion-prousar</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>ProUSAR es un proyecto GIZ vigente (actualizado febrero 2025) que apoya la transición de Colombia hacia economía circular con enfoque upstream: ecodiseño, producción eficiente y uso de recursos en sectores textil, envases/empaques y electrónicos. Cuenta con €6,8 millones de compromiso financiero. Trabaja innovación, diseño y optimización en fases tempranas de la cadena.</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Máxima pertinencia: ProUSAR trabaja exactamente en envases y empaques, ecodiseño y optimización upstream, temas centrales de Visión Circular. Es proyecto vigente con presupuesto activo y presencia en Colombia.</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pilotos de ecodiseño de envases y empaques; asistencia técnica para empresas en reciclabilidad; innovación en producción circular; articulación con sectores prioritarios de ANDI; apoyo a cumplimiento REP mediante diseño mejorado</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Alineación con objetivos del proyecto (ecodiseño, upstream, sectores textil/envases/electrónicos); actores colombianos (empresas, gremios, universidades)</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>GIZ Colombia, Ministerio de Ambiente, empresas de envases y empaques asociadas a ANDI, universidades con investigación en diseño, centros tecnológicos</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>No se especifica mecanismo de acceso a recursos; puede requerir articulación institucional previa con GIZ; no está claro si hay convocatorias abiertas o si el apoyo es vía alianza estratégica</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Contactar oficina GIZ Colombia / equipo ProUSAR para explorar articulación formal con Visión Circular ANDI, identificar líneas de cooperación en envases/empaques, ecodiseño y pilotos empresariales</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con coordinación ProUSAR (GIZ Colombia) para presentar portafolio Visión Circular y explorar sinergias, posibles pilotos conjuntos y asistencia técnica</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos / Alianzas con cooperación internacional</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Proyecto confirmado, vigente, actualizado febrero 2025, con presupuesto asignado. No es una convocatoria abierta sino un proyecto en ejecución, pero ofrece asistencia técnica y cooperación directa. Alta probabilidad de articulación institucional ANDI-GIZ.</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>0a517435c68d1ab0</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VC-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CircularEconomy4Colombia (CE4C) - Agrichallenge</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CGIAR / NATURE+ Initiative / FAO (aliados múltiples)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Colombia (nacional y global con soluciones aplicables a Colombia)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Residuos agroindustriales, valorización de residuos, conversión a energía, alimentación animal, tratamiento de aguas, suelo</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Aceleración; Innovación; Piloto demostrativo; Asistencia técnica; Premio o challenge</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Alineado con CBD COP 16 Colombia y Plan Nacional de Desarrollo 2022-2026; convocatoria activa en 2025-2026</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://agritechchallenge.org/projects/circulareconomy-4colombia</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>https://sti-portal.fao.org/innovations/circular-economy-colombia</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>CE4C es una plataforma programática de aceleración de emprendimientos y soluciones de economía circular en Colombia. El Agrichallenge busca soluciones early-stage para valorización de residuos agroindustriales (conversión a energía, alimentación animal, tratamiento de aguas, mejora de suelos). Ofrece mentoría, entrenamiento empresarial, financiamiento y networking. Basado en alianza con SENA (118 centros nacionales) y evolución de Recicle+ Network.</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Alta pertinencia para Visión Circular ANDI: economía circular territorial, valorización de residuos (incluidos residuos de envases y empaques en sector agroindustrial), modelos de negocio circulares, innovación y pilotos empresariales.</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pilotos de valorización de residuos de envases agroindustriales; innovación en conversión de residuos orgánicos con impacto en cadenas de envasado; articulación con empresas ANDI sector alimentos/bebidas; modelos circulares territoriales</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Soluciones innovadoras early-stage aplicables a Colombia; alineación con áreas prioritarias (residuos, agua, energía, suelo, alimentación animal); emprendedores o investigadores CGIAR con enfoque empresarial</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>SENA, CGIAR, empresas agroindustriales ANDI, universidades con investigación agro, cooperativas de recicladores, gobiernos locales</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Enfoque en sector agroindustrial puede no cubrir todos los subsectores de Visión Circular (envases urbanos); convocatoria no especifica fechas exactas de cierre</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Explorar articulación con CE4C para pilotos conjuntos en envases/empaques sector agroindustrial; promover participación de empresas ANDI en la plataforma; identificar sinergias con Recicle+ Network y SENA</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Contactar coordinadores CE4C Agrichallenge (https://agritechchallenge.org) para confirmar fechas de aplicación 2025-2026 y requisitos; evaluar empresas ANDI elegibles</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Coordinación de innovación / Alianzas sectoriales (agroindustria)</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Plataforma activa y vigente con múltiples aliados. No es una convocatoria cerrada sino un programa continuo con challenges específicos. Fechas no exactas pero contexto de CBD COP 16 Colombia y Plan Nacional sugiere vigencia 2025-2026. Requiere confirmación de ventanas de aplicación. | Fuente fuera del listado oficial conocido (agritechchallenge.org): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>24701c99b29754d7</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VC-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Too Good to Waste - IDB (Banco Interamericano de Desarrollo)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Banco Interamericano de Desarrollo (BID)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Regional (América Latina y Caribe)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Residuos sólidos / Economía circular</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Reducción de emisiones de metano, gestión de residuos sólidos, economía circular, recuperación de residuos</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Cofinanciación; Financiamiento concesional; Asistencia técnica; Investigación aplicada</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Más de 37 millones USD solicitados en estudios de preparación; 4 mil millones USD anuales requeridos en LAC para inversión, operación y mantenimiento</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Sí - BID explora cofinanciación con GEF (ISLANDS Caribbean Incubator Facility) y #SinDesperdicio (sector privado)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Selección de 18 finalistas de 156 propuestas elegibles ya realizada; próximas convocatorias no especificadas</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://www.ccap.org/post/latin-america-and-the-caribbean-countries-seek-to-reduce-methane-emissions-in-the-solid-waste-sector</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Too Good to Waste es una iniciativa del BID financiada por Global Methane Hub y AquaFund para mejorar gestión de residuos sólidos y reducir metano en LAC. Ya seleccionó 18 finalistas de 12 países de 156 propuestas elegibles. BID ofrece recursos para pre-inversión, inversión, sostenibilidad financiera y fortalecimiento institucional. Busca cofinanciación con GEF y sector privado. Gran demanda regional: +$4 mil millones anuales requeridos.</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Pertinente para Visión Circular ANDI: gestión de residuos sólidos (incluidos envases y empaques), economía circular, recuperación de materiales, fortalecimiento institucional y modelos de negocio circulares. Enfoque en infraestructura y cierre de ciclos.</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pre-inversión y estudios de factibilidad para proyectos de reciclaje y recuperación de envases/empaques; fortalecimiento institucional en gestión de residuos; modelos de participación privada en reciclaje; articulación con municipios para sistemas REP</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Proyectos enfocados en reducción de metano y mejora de gestión de residuos sólidos; demostrar potencial de recuperación de materiales y economía circular; alineación con objetivos BID; capacidad de cofinanciación</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>No especificado (convocatoria ya cerrada para ronda actual)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>BID, gobiernos locales (municipios), empresas sector privado (#SinDesperdicio), cooperativas de recicladores, universidades, GEF ISLANDS</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Convocatoria actual ya cerrada (18 finalistas seleccionados); próximas rondas no confirmadas; alta competencia (156 propuestas elegibles); requiere cofinanciación significativa</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Monitorear próximas convocatorias Too Good to Waste (BID); preparar cartera de proyectos pre-inversión en reciclaje y recuperación de envases con municipios; explorar alianza con #SinDesperdicio para cofinanciación sector privado</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Contactar oficina BID Colombia para conocer calendario de próximas convocatorias Too Good to Waste y requisitos de elegibilidad; mapear proyectos ANDI/Visión Circular susceptibles de pre-inversión</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos / Alianzas con banca multilateral</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Iniciativa confirmada y vigente del BID, pero la convocatoria mencionada ya seleccionó finalistas. No hay fechas de próximas rondas. Alta demanda y competencia. Cofinanciación es clave. Requiere seguimiento para futuras ventanas de aplicación. | Fuente fuera del listado oficial conocido (ccap.org): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>94e5bdfe53d8c23b</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VC-0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Circulate Capital - Financiamiento para cadenas de reciclaje</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Circulate Capital</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Fondo ambiental</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sur y Sudeste Asiático (India, Indonesia, Tailandia, Malasia, Vietnam, Filipinas); exploración oportunística en América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Reciclaje / Economía circular</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Cadenas de suministro de reciclaje, recolección y clasificación, tecnologías de upcycling, digitalización, trazabilidad</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Financiamiento concesional; Grant no reembolsable; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2 a 30 millones USD por inversión</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente (rolling basis)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://www.circulatecapital.com/apply-for-funding</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Circulate Capital invierte en empresas y tecnologías que transforman cadenas de suministro de plásticos a escala: recolección, clasificación, upcycling, digitalización, trazabilidad. Tickets de USD 2-30 millones vía equity, quasi-equity y deuda para proyectos early-growth y growth stage. Geografía prioritaria: Asia; exploración oportunística en América Latina y Caribe. Busca retornos financieros competitivos ajustados a riesgo y impacto en sostenibilidad, clima y medios de vida.</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Altamente pertinente: financiamiento para escalar cadenas de reciclaje de plásticos, tecnologías de clasificación y upcycling, digitalización y trazabilidad de materiales reciclados; temas alineados con REP, cierre de ciclos y reciclabilidad de envases.</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Escalamiento de sistemas de recolección y clasificación de envases y empaques en Colombia; tecnologías de upcycling de plásticos flexibles; digitalización de cadenas de reciclaje; trazabilidad para cumplimiento REP; fortalecimiento de cooperativas de recicladores con tecnología</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Empresas o tecnologías financieramente atractivas, retornos ajustados a riesgo; stage early-growth o growth; foco en plásticos y cadenas de reciclaje; preferiblemente Asia, pero exploran LAC oportunísticamente</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aplicación online (formulario en sitio web); plan de negocio; proyecciones financieras; descripción de impacto</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Empresas colombianas de reciclaje y clasificación, empresas de tecnología de trazabilidad, cooperativas de recicladores formalizadas, empresas de envases ANDI con interés en invertir en cadena de reciclaje</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Prioridad geográfica es Asia; América Latina es 'oportunística' (no prioritaria); requiere madurez empresarial (early-growth/growth), no apoya proyectos semilla; tickets grandes (USD 2-30M) pueden excluir iniciativas pequeñas; retornos financieros competitivos obligatorios</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Identificar empresas colombianas de reciclaje/clasificación con potencial de escala y retornos financieros; preparar casos de negocio robustos para presentar a Circulate Capital; explorar coinversión con empresas ANDI</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Mapear empresas reciclaje Colombia elegibles (early-growth/growth); contactar Circulate Capital vía formulario online para expresar interés y evaluar apetito por proyectos Colombia; preparar pitch financiero y de impacto</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Alianzas estratégicas / Desarrollo de negocios / Atracción de inversión</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Fondo confirmado, activo y abierto permanentemente. Sin embargo, América Latina no es prioridad geográfica (solo oportunístico). Requiere madurez empresarial alta y retornos financieros competitivos. Tickets grandes. Baja probabilidad para proyectos ANDI directos, pero posible para empresas asociadas maduras.</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>2b53b10aaeeff5cd</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VC-0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Collateral Good Packaging Innovation Fund I</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Collateral Good</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Fondo ambiental</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Europa (Unión Europea)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Global (North America, Europe, Latin America explícitamente mencionados)</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Envases y empaques, innovación en packaging sostenible, reciclabilidad, sistemas de reutilización</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Financiamiento concesional; Innovación; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>EUR 500,000 a EUR 2,500,000 por empresa</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>https://collateralgood.eu/sustainable-investing-funds/collateral-good-packaging-innovation-fund-i</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Fondo de inversión global enfocado en innovación en packaging sostenible y economía circular. Invierte en startups late-seed a Series A (10-12 empresas) con tickets de EUR 500K-2.5M. Busca soluciones en conectividad de envases, circularidad, ingredientes bioprocesados, packaging reutilizable y sistemas ERP para negocios circulares. América Latina es explícitamente mencionada como región de inversión.</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Altamente relevante: financia soluciones de packaging circular, reciclabilidad, reutilización y sistemas para gestión de economía circular. Alineado con ecodiseño, cierre de ciclo de envases y modelos de negocio circulares que promueve Visión Circular.</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pilotos de packaging reutilizable para sectores industriales; tecnologías de trazabilidad de envases; soluciones de reciclabilidad para plásticos flexibles; plataformas digitales para gestión circular de empaques; innovaciones en biomateriales para envases; modelos de negocio de retorno y reutilización</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Startups en fase late-seed a Serie A con soluciones innovadoras en packaging sostenible o economía circular. Modelo de negocio escalable con potencial de impacto ambiental verificable</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>No especificado (típicamente: pitch deck, plan de negocio, proyecciones financieras, métricas de impacto ambiental)</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Empresas ANDI con líneas de packaging; startups colombianas de tecnología circular; centros de innovación como Ruta N, Connect Bogotá; universidades con grupos de ecodiseño (EAFIT, Andes, Nacional); Innpulsa Colombia</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Fondo busca empresas en etapas tempranas (late-seed/Series A), no proyectos gremiales o de asistencia técnica directa. Visión Circular ANDI tendría que estructurar vehículo empresarial o spin-off para aplicar, o identificar startups colombianas para recomendar/acompañar</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Mapear startups colombianas en packaging circular elegibles y ofrecerles acompañamiento técnico de Visión Circular para fortalecer postulación. Explorar co-creación de spin-off empresarial con empresas ANDI para acceder al fondo. Establecer contacto con Collateral Good para entender criterios de inversión en Latam</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Contactar a Collateral Good (vía web/newsletter) para solicitar criterios detallados de inversión y fechas de convocatoria. Iniciar mapeo de startups colombianas elegibles en portafolio Visión Circular y aliados (Apps.co, iNNpulsa, universidades)</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Coordinación de innovación y alianzas empresariales; área de nuevos modelos de negocio</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>No hay convocatoria abierta publicada ni fechas, pero el fondo está activo con portafolio en construcción (10-12 empresas objetivo). América Latina es región explícita de inversión. Requiere verificar proceso de aplicación y si aceptan postulaciones continuas o por rondas. Podría ser oportunidad indirecta: Visión Circular como facilitador/acelerador de startups colombianas hacia este fondo | Fuente fuera del listado oficial conocido (collateralgood.eu): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>244e1938643fce18</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VC-0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Too Good to Waste Initiative - IDB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Banco Interamericano de Desarrollo (BID/IDB)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Regional - América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>América Latina y el Caribe (Colombia elegible)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Residuos</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Economía circular, gestión de residuos, mitigación de metano, resiliencia climática</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Cooperación técnica; Asistencia técnica; Financiamiento concesional; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Iniciativa de mediano-largo plazo, sin convocatoria puntual publicada</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>https://www.iadb.org/en/who-we-are/topics/water-and-sanitation/initiatives/too-good-waste</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Iniciativa del BID para mejorar gestión de residuos en ALC, avanzar hacia economía circular competitiva, construir resiliencia ante clima extremo y reducir emisiones de metano. Estructura proyectos y promueve condiciones habilitantes en el sector de residuos. Enfoque en transición desde modelo lineal (extracción-consumo-disposición) hacia circularidad y recuperación de recursos.</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Altamente relevante: aborda economía circular en residuos, gestión de envases post-consumo (parte integral del sistema de residuos), condiciones habilitantes para REP, y cierre de ciclo de materiales. BID es socio estratégico de ANDI y gobiernos en Colombia para financiar infraestructura circular</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Proyectos de infraestructura para reciclaje y separación de envases; sistemas de recolección y clasificación de residuos de envases; fortalecimiento institucional para implementación REP; economía circular territorial en municipios; captura y aprovechamiento de metano en rellenos (con co-beneficio de reducción huella envases); estudios de factibilidad para plantas de reciclaje químico de plásticos</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Típicamente: solicitud de gobiernos nacionales/locales o entidades públicas; puede incluir sector privado vía APP (Alianzas Público-Privadas); alineación con prioridades nacionales (NDC, estrategias residuos/economía circular); capacidad de contrapartida; sostenibilidad financiera del proyecto</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>No especificado (proyectos BID típicamente requieren: ficha de proyecto, análisis de viabilidad, presupuesto detallado, plan de sostenibilidad, estudios técnicos, cartas de compromiso institucional)</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Ministerio de Ambiente y Desarrollo Sostenible; Ministerio de Vivienda; gobiernos locales (Bogotá, Medellín, Cali, Barranquilla, otras ciudades con metas REP); empresas ANDI del sector envases; gremios (Acoplásticos, Cempre); universidades para componentes técnicos; asociaciones de recicladores</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Iniciativa marco sin convocatoria específica abierta en este momento. Acceso típicamente requiere articulación gobierno-BID, puede ser proceso largo (12-24 meses). No es grant directo sino financiamiento/cooperación que requiere estructura institucional robusta</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Articular reunión entre ANDI/Visión Circular, Ministerio de Ambiente y BID Colombia para identificar ventanas de financiamiento específicas bajo 'Too Good to Waste' aplicables a implementación REP de envases, infraestructura de reciclaje o economía circular territorial. Preparar concept note de proyecto</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Contactar al representante BID Colombia (División Agua y Saneamiento) para agendar reunión exploratoria. Solicitar información sobre pipeline de proyectos en residuos/economía circular 2026-2027 y cómo Visión Circular puede articularse</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Dirección ejecutiva / Coordinación de proyectos estratégicos; área de relaciones con banca multilateral</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Iniciativa estratégica del BID confirmada y vigente, pero no es convocatoria abierta específica sino marco programático. Acceso requiere articulación institucional gobierno-BID-sector privado. Alta pertinencia porque BID es socio natural de Colombia para financiar infraestructura circular y REP. Probabilidad 4 (no 5) porque requiere mediación gubernamental y proceso de estructuración de proyecto</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>aa53a3d2daa23a2d</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VC-0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Unlocking Innovation in Circular Plastics in the LATAM region 2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>WRAP y Plastics Pact Network</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>América Latina (región)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Plásticos flexibles, Envases y empaques, Reciclaje, Ecodiseño</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Aceleración; Grant no reembolsable; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Hasta USD 10,000 por solución (hasta 3 mini-grants)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2025 (año en curso, sin fecha exacta)</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>https://www.wrap.ngo/take-action/plastic-pact-network/innovation-circular-plastics-latam-2025</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>WRAP y la Red de Pactos de Plásticos buscan apoyar 10 soluciones innovadoras que aborden desafíos críticos para acelerar la circularidad de plásticos en América Latina, con foco en envases y plásticos flexibles con alto riesgo de fuga al océano. Las soluciones seleccionadas recibirán un programa de fortalecimiento de capacidades y hasta 3 mini-grants de USD 10,000 cada uno para acercar sus soluciones a inversión y pruebas reales. Los desafíos cubren reducción de plásticos flexibles problemáticos, reciclabilidad mediante diseño y tecnologías intermedias, y mercados finales para PP y poliolefinas recicladas.</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Altamente pertinente para Visión Circular ANDI: aborda plásticos flexibles (línea prioritaria del programa), ecodiseño, reciclabilidad, y cierre de ciclo en envases y empaques. Los desafíos están completamente alineados con REP, inclusión de tecnologías de reciclaje y economía circular territorial.</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pilotos de reciclaje de plásticos flexibles multicapa; desarrollo de mercados para poliolefinas recicladas; innovación en ecodiseño de envases flexibles monomateriales; tecnologías intermedias para recuperación de sachets y films; modelos de negocio circulares para empaques flexibles con inclusión de recicladores; soluciones para reducción de contaminación marina por plásticos flexibles.</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Soluciones deben enfocarse en envases y plásticos flexibles con alto riesgo de fuga oceánica; abordar uno o más de los 3 desafíos (reducción de flexibles problemáticos, reciclabilidad mediante diseño/tecnología, mercados finales para PP/PE reciclados); aplicables a América Latina; ser innovadoras y escalables.</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Acoplásticos (gremio plásticos Colombia); empresas de envases flexibles; startups de reciclaje químico como Polyrec, Esenttia; universidades con líneas en materiales (EAFIT, Andes, Nacional); recicladores formales e informales; Pacto de Plásticos Colombia (si existe o en formación).</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Fecha de cierre no especificada en la fuente; posible alta competencia regional; mini-grants limitados (solo 3 de 10 seleccionados); puede requerir capacidad previa en plásticos técnicos.</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Contactar inmediatamente a WRAP para confirmar plazos y requisitos exactos de aplicación; preparar portafolio de soluciones o empresas colombianas en plásticos flexibles que puedan aplicar; identificar 2-3 proyectos prioritarios de Visión Circular que encajen en los 3 desafíos.</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Escribir hoy a WRAP vía formulario web o contacto en página oficial solicitando plazos, términos de referencia y eligibilidad para entidades colombianas/ANDI; convocar reunión interna esta semana para mapear soluciones candidatas.</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos / Innovación de Visión Circular ANDI; Alianzas internacionales</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Oportunidad de altísima pertinencia y eligibilidad directa para Colombia. Los 3 desafíos mencionados coinciden exactamente con líneas de trabajo de Visión Circular. La fecha '2025' sugiere ventana abierta o próxima, pero debe verificarse plazo exacto. WRAP es organización de referencia global en economía circular de plásticos. | Fuente fuera del listado oficial conocido (wrap.ngo): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>f0e4e507b1c4b1d1</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VC-0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IFC &amp; BFS Industrial Plastic Circularity in Latin America</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>International Finance Corporation (IFC) y BlackForest Solutions GmbH, en colaboración con ABIPLAST</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Internacional (IFC - Grupo Banco Mundial)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>América Latina y el Caribe (LAC), con énfasis en Brasil</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Plásticos industriales, Circularidad, Reducción de huella de plástico, Inversión sostenible</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Cooperación técnica; Asistencia técnica; Financiamiento concesional; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2025-2026 (en implementación desde anuncio 2025/2026)</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>No especificado (programa plurianual)</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>https://rainbowforest.org/bfs/ifc-bfs-plastic-circularity-latin-america-2026</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>IFC ha lanzado una iniciativa regional para acelerar la circularidad de plásticos industriales en América Latina y el Caribe, implementada por BlackForest Solutions GmbH en colaboración con ABIPLAST (asociación de plásticos de Brasil). El programa ayuda a empresas a medir huellas de plástico, diseñar hojas de ruta de reducción y construir proyectos circulares listos para inversión. Busca desbloquear financiamiento para infraestructura circular y estrategias corporativas de sostenibilidad. La región produce 15.7 millones de toneladas anuales; Brasil recicló &gt;20% en 2024.</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Altamente relevante: programa diseñado para apoyar economía circular de plásticos a nivel empresarial y de gremios en América Latina. ANDI podría posicionarse como socio estratégico en Colombia (equivalente a ABIPLAST en Brasil) para articular empresas colombianas con este programa IFC, especialmente para acceder a financiamiento concesional y asistencia técnica en proyectos circulares.</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medición de huella de plásticos en empresas asociadas a ANDI; diseño de hojas de ruta de reducción y circularidad para sectores prioritarios (alimentos, cosméticos, retail); estructuración financiera de proyectos de reciclaje químico o mecánico; inversión en infraestructura de recuperación y clasificación de plásticos; desarrollo de cadenas de valor circulares regionales.</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Empresas operando en Brasil y América Latina que busquen reducir huellas de plástico o desarrollar estrategias de inversión en economía circular; disponibilidad de datos operacionales para medición; compromiso corporativo con metas circulares.</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>No especificado (probablemente: datos de consumo de plásticos, información corporativa, estrategia de sostenibilidad, capacidad de cofinanciación)</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>IFC Colombia; Acoplásticos; Cámaras empresariales ANDI; empresas con alta huella de plástico (Alpina, Colombina, Postobón, Grupo Nutresa); BlackForest Solutions; ABIPLAST (para aprendizaje Sur-Sur); BID Lab; centros tecnológicos como ICIPC.</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Programa aún en fase de mapeo y línea base; puede requerir que empresas tengan capacidad de inversión o cofinanciación; prioridad puede estar en Brasil dado el socio ABIPLAST; información limitada sobre proceso de acceso.</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Contactar oficina IFC Colombia para explorar colaboración como gremio y entidad articuladora en Colombia; ofrecer a ANDI como socio estratégico equivalente a ABIPLAST; identificar 5-10 empresas colombianas candidatas con alta huella de plástico para fase piloto.</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con IFC Colombia esta semana; preparar one-pager de Visión Circular y su red empresarial; contactar a BlackForest Solutions vía LinkedIn o web para expresar interés de articulación en Colombia.</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Dirección de Visión Circular ANDI; Gerencia de sostenibilidad ANDI; Relaciones institucionales con banca multilateral</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Iniciativa estratégica de IFC altamente alineada con misión de Visión Circular. El programa está en fase temprana de implementación (mapeo y línea base), lo que representa ventana de oportunidad para posicionar a ANDI como socio en Colombia. La colaboración con ABIPLAST indica preferencia por trabajar con gremios sectoriales. Eligibilidad alta pero requiere acción proactiva para asegurar participación colombiana más allá de Brasil. | Fuente fuera del listado oficial conocido (rainbowforest.org): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>2fc6da8646a431a1</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VC-0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Too Good to Waste - Call for initiatives to mitigate methane emissions from solid waste sector</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Inter-American Development Bank (IDB)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Regional - América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Residuos</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Mitigación de metano, Economía circular de residuos, Gestión de residuos sólidos, Cambio climático</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Cooperación técnica; Innovación; Piloto demostrativo</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>https://www.iadb.org/en/how-we-can-work-together/calls-proposals</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>El BID ha lanzado una convocatoria para iniciativas orientadas a mitigar emisiones de metano del sector de residuos sólidos en América Latina y el Caribe. La convocatoria busca soluciones innovadoras que reduzcan emisiones de gases de efecto invernadero desde la gestión de residuos, alineada con compromisos climáticos regionales. Aunque la información es limitada, es parte del portafolio activo de convocatorias del BID.</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Pertinente para Visión Circular: la gestión circular de residuos de envases y empaques puede contribuir a reducir metano al desviar residuos orgánicos y materiales de rellenos sanitarios, promoviendo reciclaje, compostaje y valorización. Conexión con economía circular territorial y articulación con autoridades locales en gestión de residuos.</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Proyectos de desvío de residuos orgánicos de envases post-consumo; valorización de residuos de empaques mediante reciclaje para evitar disposición final; sistemas de recolección diferenciada con inclusión de recicladores para reducir metano; pilotos de captura de metano en rellenos con co-beneficios circulares; educación y sensibilización para reducción de residuos en origen.</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>No especificado (probablemente: startups, pymes, organizaciones sociales, universidades, gobiernos locales de LAC; proyectos con impacto medible en reducción de metano; innovación y escalabilidad)</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Municipios y autoridades ambientales regionales; organizaciones de recicladores; empresas de gestión de residuos; centros de investigación en gases de efecto invernadero; ANDI empresas del sector alimentos y bebidas (grandes generadores de residuos orgánicos en envases).</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Información muy limitada en fuente; no se especifican plazos, montos ni proceso de aplicación; puede estar cerrada o en diseño; requiere verificación urgente de vigencia.</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Visitar página oficial de convocatorias BID y buscar términos de referencia completos; contactar oficina BID Colombia para confirmar vigencia y obtener información detallada; si está abierta, mapear proyectos de Visión Circular con componente de reducción de metano.</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Acceder hoy a https://www.iadb.org/en/how-we-can-work-together/calls-proposals y buscar 'Too Good to Waste' o 'methane'; contactar representante BID Colombia vía correo institucional solicitando información.</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos; Gestión de residuos / Economía circular territorial</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Convocatoria aparece listada en página activa de BID pero sin detalles. La mitigación de metano no es foco directo de Visión Circular pero hay conexiones indirectas fuertes vía gestión circular de residuos. Pertinencia media-alta si se enfoca en circularidad de envases; probabilidad media por falta de información de acceso.</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>a588e9c9c30bb94d</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VC-0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AGRInnova - Call for Proposal</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Inter-American Development Bank (IDB)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Regional - América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>América Latina y el Caribe</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sostenibilidad empresarial</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Agronegocios, Sostenibilidad operacional, Mitigación y adaptación climática, Productividad</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Cooperación técnica; Innovación; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>https://www.iadb.org/en/how-we-can-work-together/calls-proposals</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Iniciativa del BID para apoyar agronegocios en América Latina y el Caribe a aumentar productividad, eficiencia y sostenibilidad operacional frente a riesgos de cambio climático. Busca mitigación y adaptación climática en el sector agroindustrial mediante innovación y mejores prácticas.</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pertinencia moderada: no es foco principal de Visión Circular, pero agronegocios son grandes usuarios de envases y empaques (agroquímicos, alimentos procesados, bebidas). Posible articulación si se enfoca en economía circular de envases agroindustriales, reducción de plásticos de un solo uso en agricultura, o modelos circulares en cadenas agroalimentarias (packaging sostenible).</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Economía circular de envases en cadenas agroalimentarias asociadas a ANDI; reducción de empaques plásticos en agroindustria; sistemas de retorno de envases de agroquímicos; ecodiseño de empaques para productos agrícolas de exportación; pilotos de empaque reutilizable en frutas y flores.</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No especificado (probablemente: agronegocios de LAC; proyectos con impacto en sostenibilidad y clima; innovación)</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Empresas agroalimentarias asociadas a ANDI (Alpina, Postobón, Nutresa, Riopaila); gremios agrícolas; universidades con facultades de agronomía; proveedores de empaques para agricultura.</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Pertinencia indirecta para mandato central de Visión Circular; información limitada; puede no estar abierta o tener foco muy específico en producción agrícola sin énfasis en envases.</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Verificar si convocatoria acepta proyectos de economía circular de envases agroindustriales; si sí, considerar proyecto piloto con empresa agroalimentaria de ANDI; si no, descartar por baja pertinencia.</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Consultar términos completos en página BID; si no hay fit claro con envases/empaques, pasar a otras oportunidades más prioritarias.</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos (evaluación preliminar)</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Oportunidad de baja-media pertinencia para Visión Circular. Solo aplicable si se puede articular circularidad de envases en agroindustria. Prioridad baja frente a otras convocatorias más alineadas. Falta información crítica de acceso.</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>2f783fc9916c84a2</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VC-0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Caribbean Loans Call for Proposals - IDB Lab</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IDB Lab (Inter-American Development Bank)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Banca multilateral</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Regional - Caribe</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Caribe (6 países objetivo, más 48 países miembros del BID pueden aplicar si implementan en los 6 países Caribe objetivo)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sostenibilidad empresarial</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Inclusión financiera, Resiliencia climática, Impacto social, Innovación</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Financiamiento concesional; Innovación; Escalamiento</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>No especificado (préstamos, no grants)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>https://bidlab.org/en/home/caribbean-loans-call-proposals</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>IDB Lab busca identificar candidatos elegibles para financiamiento de deuda (préstamos) en el Caribe. Busca empresas en la intersección de impacto, innovación y sostenibilidad financiera, apoyando pymes y organizaciones de base que trabajen en inclusión financiera, resiliencia climática e impacto social. Empresas deben estar en operación, generar ingresos y buscar financiamiento de deuda para escalar proyectos con impacto demostrable.</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pertinencia baja-media: foco geográfico es Caribe, no Colombia directamente; sin embargo, empresas colombianas registradas en países BID pueden aplicar si implementan en Caribe. Posible si Visión Circular/ANDI tiene proyectos de economía circular de envases con expansión Caribe (ej. San Andrés, o alianzas con islas caribeñas). Resiliencia climática puede incluir gestión de residuos y circularidad.</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Expansión de modelos de reciclaje inclusivo de envases a islas del Caribe con vulnerabilidad a contaminación plástica marina; proyectos de economía circular de plásticos en San Andrés y Providencia (territorio colombiano Caribe); alianzas con empresas caribeñas para sistemas de retorno de envases; infraestructura de reciclaje en pequeñas islas.</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Empresas con fines de lucro, en operación, generando ingresos, buscando deuda (no grant); registradas en países miembros BID; implementación en 6 países Caribe objetivo; modelo de negocio sólido con potencial de crecimiento y sostenibilidad financiera; impacto social/ambiental demostrable.</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>No especificado (probablemente: estados financieros, plan de negocio, modelo de impacto, registro legal)</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Empresas de reciclaje con proyectos en San Andrés; startups colombianas de economía circular con potencial de expansión caribeña; autoridades ambientales de San Andrés; socios caribeños del Plastics Pact Network.</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Foco geográfico fuera de Colombia continental; requiere presencia o alianza en Caribe; financiamiento es deuda (reembolsable), no grant; empresas deben tener capacidad de repago; pertinencia limitada para mandato central de Visión Circular.</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Evaluar si hay empresas en red Visión Circular con operaciones o expansión planeada en Caribe (incluido San Andrés); si sí, explorar eligibilidad; si no, descartar por baja pertinencia geográfica.</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Revisar portafolio de empresas asociadas a Visión Circular con presencia Caribe; si hay candidatos, contactar IDB Lab; si no, archivar como no prioritaria.</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Alianzas empresariales / Desarrollo de negocios (evaluación preliminar)</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Oportunidad de baja pertinencia para Visión Circular debido a foco geográfico Caribe y naturaleza de deuda (no grant). Solo aplicable si hay proyectos específicos de expansión caribeña. San Andrés podría ser puente, pero requiere caso de negocio sólido. Prioridad baja.</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>9353a162e964de0b</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VC-0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GEF Small Grants Programme (SGP) - Colombia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Global Environment Facility (GEF) implementado por UNDP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fondo ambiental</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Colombia (programa específico colombiano)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Biodiversidad, Cambio climático, Degradación de tierras</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Conservación, Gestión ambiental comunitaria, Sostenibilidad local</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Hasta USD 50,000 por proyecto (histórico: hasta USD 15,000 para organizaciones comunitarias, hasta USD 35,000 para organizaciones con experiencia)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No especificado (programa permanente con ventanas periódicas)</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>No especificado (requiere verificación con oficina Colombia)</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>https://www.thegef.org/what-we-do/topics/gef-small-grants-program</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>https://www.thegef.org/newsroom/news/gef-small-grants-programme-launched-colombia</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>El Programa de Pequeñas Donaciones del GEF apoya a organizaciones de sociedad civil y comunitarias para desarrollar e implementar acciones locales innovadoras que aborden problemas ambientales globales (biodiversidad, cambio climático, degradación de tierras, químicos, aguas internacionales), mejorando al mismo tiempo medios de vida y reduciendo pobreza. En Colombia, el programa fue lanzado oficialmente en 2015 y ofrece grants de hasta USD 50,000 (montos varían según experiencia de organización).</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pertinencia media: el GEF SGP tradicionalmente se enfoca en biodiversidad, bosques y áreas rurales, pero en fase GEF-7 y GEF-8 ha incorporado economía circular, gestión de residuos y químicos. Posible articulación para proyectos de economía circular territorial con enfoque comunitario, inclusión de recicladores de base, gestión de residuos plásticos en territorios vulnerables, o pilotos de recuperación de envases en paisajes prioritarios.</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pilotos de reciclaje inclusivo de envases en comunidades rurales o periurbanas; sistemas de recuperación de plásticos en zonas costeras o cuencas hidrográficas (enfoque océano-residuos); fortalecimiento de organizaciones de recicladores de base con enfoque de economía circular; educación ambiental y gestión comunitaria de residuos de envases en territorios con alta biodiversidad.</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Organizaciones de sociedad civil (OSC) o comunitarias (CBO) en Colombia; proyectos de hasta USD 50,000; enfoque local con impacto ambiental global; alineación con áreas focales GEF (biodiversidad, clima, tierras, químicos, aguas); participación comunitaria; enfoque en pueblos indígenas, mujeres, juventud.</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Propuesta de proyecto (formato GEF SGP); presupuesto detallado; información legal de organización; carta de respaldo de comunidad o autoridad local; plan de participación comunitaria; indicadores de impacto ambiental y social.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Organizaciones de recicladores de base; asociaciones comunitarias en regiones de alto valor ecológico; ONGs ambientales locales; universidades con presencia regional; autoridades ambientales regionales (CAR); UNDP Colombia (implementador).</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Montos limitados (máx USD 50,000); proceso puede ser lento; requiere capacidad de organizaciones comunitarias para formulación; foco histórico en biodiversidad/bosques puede limitar aprobación de proyectos de residuos/circularidad si no se articula bien con co-beneficios ambientales; posible competencia alta.</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Contactar oficina GEF SGP Colombia (vía UNDP Colombia) para confirmar si hay ventanas abiertas y elegibilidad para proyectos de economía circular de residuos; si hay fit, identificar 2-3 organizaciones de recicladores en territorios prioritarios de ANDI para co-diseñar propuestas.</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Escribir a UNDP Colombia (GEF SGP) solicitando información sobre próximas ventanas, áreas prioritarias GEF-8 en Colombia y elegibilidad para proyectos de economía circular/residuos; reunión con área de inclusión social de Visión Circular para mapear organizaciones candidatas.</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Inclusión social / Economía circular territorial; Coordinación de proyectos</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Oportunidad válida pero de pertinencia media. GEF SGP es fuente probada de financiamiento para proyectos locales en Colombia, pero su foco tradicional no es economía circular de envases. Sin embargo, GEF-8 ha ampliado temas a químicos, residuos y economía circular. La clave es articular proyectos de reciclaje/envases con co-beneficios en biodiversidad, clima o químicos peligrosos. Montos modestos pero accesibles para pilotos comunitarios.</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>8a914eb3ab9fadf6</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VC-0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Programa Euroclima - Asistencia Técnica en Economía Circular y Gestión de Residuos (América Latina y el Caribe)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Unión Europea (implementado por Expertise France, GIZ, FIIAPP y otras agencias)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Cooperación multilateral</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Unión Europea</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>33 países de América Latina y el Caribe, incluyendo Colombia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Gestión de residuos y aguas residuales, Eficiencia en el uso de recursos, Modelos de negocio sostenibles, Plásticos, Reciclaje</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Asistencia técnica; Cooperación técnica; Financiamiento climático; Fortalecimiento institucional</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://capacity4dev.europa.eu/events/euroclima-annual-meeting-2026_en</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>https://expertise-france.gestmax.fr/_expertise_france/public_files/tdr-experto-a-guatemala-economia-circular.pdf</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>El programa Euroclima de la UE apoya a países de América Latina y el Caribe en el diseño e implementación de políticas para enfrentar el cambio climático, con énfasis actual en economía circular y transición energética. El Encuentro Anual 2026 (24-26 marzo, Panamá) priorizó fortalecer políticas públicas, movilizar inversiones verdes y acelerar acciones climáticas concretas. Expertise France busca actualmente expertos en economía circular y estructuración de proyectos de inversión para asistencia técnica en Guatemala (valorización de residuos plásticos en cuenca del Río Motagua), lo que indica líneas activas de financiación.</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Altamente relevante: Euroclima financia directamente asistencia técnica en economía circular, gestión de residuos plásticos, cadenas de reciclaje, y modelos de negocio sostenibles en América Latina. El programa busca proyectos demostrativos o estructurantes que se integren con políticas públicas nacionales en gestión de residuos, economía circular y acción climática, alineado con los ejes de Visión Circular ANDI.</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Diseño de políticas públicas de economía circular territorial en Colombia; Proyectos demostrativos de valorización de residuos plásticos flexibles; Estructuración de cadenas de reciclaje inclusivo; Articulación público-privada para cumplimiento REP; Modelos de negocio circulares en envases y empaques; Pilotos empresariales de ecodiseño y reciclabilidad.</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alineación con prioridades nacionales en gestión de residuos, economía circular y acción climática; Potencial demostrativo o estructurante para desarrollo de cadenas de reciclaje; Coherencia con políticas públicas existentes; Diálogo interinstitucional y articulación con actores locales</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>No especificado (varían según modalidad de cooperación técnica)</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Ministerios de Ambiente y Desarrollo Sostenible de Colombia; Gobierno local/departamental; Expertise France; GIZ; FIIAPP; universidades y centros tecnológicos; empresas miembros de ANDI; organizaciones de recicladores; gremios sectoriales</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Proceso de solicitud y aprobación no transparente en resultados de búsqueda; Requiere articulación política y diálogo interinstitucional previo; Tiempos de estructuración pueden ser largos; No hay claridad sobre montos ni ventanas de aplicación continuas</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Contactar inmediatamente a la Delegación de la Unión Europea en Colombia y a Expertise France para conocer ventanas activas de asistencia técnica en economía circular. Mapear proyectos demostrativos de Visión Circular susceptibles de escalar con apoyo Euroclima. Preparar concept notes alineados con NDC de Colombia y políticas de gestión de residuos.</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con punto focal Euroclima en Colombia (Delegación UE Bogotá) para presentar portafolio Visión Circular y explorar líneas de cooperación técnica específicas. Revisar Terms of Reference de Guatemala como modelo de estructuración de propuestas.</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos y alianzas internacionales de Visión Circular / ANDI</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>El Encuentro Anual 2026 ya ocurrió (24-26 marzo). Sin embargo, el programa Euroclima es continuo y las fuentes indican líneas activas de asistencia técnica (ejemplo Guatemala). No hay convocatoria abierta explícita pero el programa opera mediante diálogo país y solicitudes de asistencia técnica. La pertinencia temática es máxima. Se requiere verificación de ventanas activas específicas para Colombia. | Fuente fuera del listado oficial conocido (capacity4dev.europa.eu): verificar oficialidad</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>ea20a263fc57423b</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VC-0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UK PACT Colombia - Green Finance Call for Proposals</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Gobierno del Reino Unido (UK International Climate Finance - ICF)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Cooperación bilateral</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Colombia (organizaciones elegibles ODA)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Financiamiento climático</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Finanzas verdes, Inversiones sostenibles, Financiamiento de proyectos verdes y de naturaleza</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Asistencia técnica; Fortalecimiento institucional; Innovación</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Hasta GBP 500,000 por año fiscal</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>https://www.ukpact.co.uk/news/uk-pact-call-for-proposals-colombia-green-finance</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>https://7376512.fs1.hubspotusercontent-na1.net/hubfs/7376512/Call%20for%20Proposals%20(CfP)%20launches/Colombia/2024/GF/Colombia-UK%20PACT%20ToR%20Green%20finance%20v5.pdf</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>UK PACT Colombia busca cerrar la brecha financiera para alcanzar las metas NDC de Colombia mediante asistencia técnica y fortalecimiento de capacidades en finanzas verdes. El fondo apoya proyectos de 12-33 meses con hasta £500,000/año que aceleren la adopción de estrategias sostenibles en el sector financiero y aumenten inversiones públicas y privadas en proyectos verdes y de naturaleza. Dos áreas de intervención: (1) apoyo a adopción de estrategias sostenibles en sector financiero; (2) movilización de inversiones verdes.</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Relevante indirectamente: aunque el enfoque principal es finanzas verdes y clima, el programa UK PACT ha financiado £24 millones en Colombia desde 2018 en sectores incluyendo sostenibilidad. Visión Circular podría estructurar proyectos de financiamiento verde para modelos de negocio circulares, cadenas de reciclaje o inversiones empresariales en economía circular, presentándolos como contribución a las NDC de Colombia.</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Mecanismos financieros para escalar modelos de negocio circulares en envases; Instrumentos de financiamiento verde para empresas que cumplan REP; Estructuración de bonos verdes o fondos de inversión en economía circular; Asistencia técnica a instituciones financieras para evaluar proyectos de reciclaje y circularidad.</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Organizaciones elegibles ODA; Proyectos de 12-33 meses; Contribución a metas NDC de Colombia; Enfoque en finanzas sostenibles, adopción de estrategias verdes en sector financiero o movilización de inversiones en proyectos verdes/naturaleza</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Expression of Interest (EOI); aplicación completa (información de equipo, presupuestos, planes)</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Ministerio de Hacienda; Superintendencia Financiera de Colombia; Banca comercial y de desarrollo (Bancóldex, Findeter); Asociaciones del sector financiero (Asobancaria); empresas miembros ANDI con necesidades de financiamiento verde para economía circular</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada (deadline 15 noviembre 2024). Sin información de nuevas ventanas en 2025-2026. Enfoque principal es finanzas verdes y clima, no específicamente economía circular; requiere enmarcar proyectos circulares bajo narrativa climática/NDC.</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Contactar UK PACT Colombia para conocer si habrá nuevas convocatorias en 2026 o ventanas de financiamiento continuas. Preparar concept notes que vinculen economía circular de envases con reducción de emisiones GEI y cumplimiento de NDC colombiana. Explorar alianzas con sector financiero para co-diseñar instrumentos de financiamiento verde para economía circular.</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Escribir a UK PACT Colombia (vía web ukpact.co.uk) para consultar próximas convocatorias y elegibilidad de proyectos de economía circular bajo marco de finanzas verdes. Revisar TdR completos del PDF para entender criterios detallados.</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos y movilización de recursos; área de alianzas estratégicas</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>La convocatoria encontrada cerró en noviembre 2024. No hay evidencia en las fuentes de convocatorias activas en 2026. UK PACT opera por ventanas periódicas; históricamente ha lanzado convocatorias en Colombia en diversos sectores (2021, 2024). La pertinencia es indirecta: requiere enmarcar economía circular bajo finanzas verdes/climáticas. Se marca como requiere verificación porque la información es de 2024 y no hay confirmación de convocatorias 2026.</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>b42f16fd869be642</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VC-0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Latitud R - Plataforma Regional de Reciclaje Inclusivo (Fundación Avina)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fundación Avina, The Coca-Cola Company, PepsiCo, Dow, Nestlé, BID, BID Lab</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>América Latina (Avina), EE.UU. (empresas), BID (multilateral)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>América Latina (Brasil, México, Perú, Colombia y otros países de la región)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Reciclaje</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Reciclaje inclusivo, Inclusión de recicladores, Economía circular, Gestión de residuos, Cadenas de valor de reciclaje</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Cofinanciación; Asistencia técnica; Fortalecimiento institucional; Innovación; Piloto demostrativo; Escalamiento; Inclusión social</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Sí, modelo de colaboración multisectorial con alineación de agendas y co-inversión</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente (plataforma continua)</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Abierta permanentemente</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>https://latitudr.org</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://www.avina.net/wp-content/uploads/2022/11/LATITUD-R-GAINS-STRENGTH-AS-A-REGIONAL-PLATFORM-TO-SCALE-UP-INCLUSIVE-RECYCLING-AND-MOVE-TOWARD-A-CIRCULAR-ECONOMY.pdf</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Latitud R es una plataforma regional de colaboración multisectorial liderada por Fundación Avina que impulsa el reciclaje inclusivo en América Latina. Reúne empresas privadas (Coca-Cola, PepsiCo, Dow, Nestlé), agencias de desarrollo (BID, BID Lab) y organizaciones de recicladores para co-invertir en iniciativas, alinear agendas y escalar impactos. El modelo incluye a recicladores en la toma de decisiones. Actualmente activa en Brasil, México, Perú y otros países con proyectos de fortalecimiento organizativo, infraestructura de acopio, comercialización, salud, emprendimiento y liderazgo de mujeres recicladoras.</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Altamente pertinente: Latitud R aborda directamente inclusión de recicladores, cierre de ciclo de envases/empaques, cadenas de valor de reciclaje y economía circular inclusiva. Su modelo de colaboración empresas-recicladores-desarrollo es coherente con los ejes de Visión Circular ANDI. Oportunidad para articular la agenda empresarial de REP y reciclabilidad de envases con inclusión social y fortalecimiento de cadenas de reciclaje de base comunitaria.</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de organizaciones de recicladores en Colombia; Infraestructura de centros de acopio y comercialización de materiales reciclables; Pilotos de reciclaje de plásticos flexibles con inclusión de recicladores; Articulación empresas-recicladores para cierre de ciclo de envases; Capacitación en finanzas, emprendimiento y comercialización para recicladores; Modelos de negocio circulares inclusivos.</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alineación con agenda de reciclaje inclusivo y economía circular; Colaboración multisectorial (empresas, organizaciones de recicladores, gobierno, academia); Enfoque en dignificación del trabajo de recicladores; Potencial de escalamiento regional; Contribución a metas de gestión de residuos y sostenibilidad</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>No especificado (requiere contacto directo con Fundación Avina y Latitud R)</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Fundación Avina; Red Latinoamericana de Recicladores; empresas de envases y empaques miembros de ANDI (Coca-Cola, PepsiCo, Nestlé, Dow presentes en Colombia); BID y BID Lab; organizaciones de recicladores colombianos; Ministerio de Ambiente; gobiernos locales</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Modelo de gobernanza complejo (múltiples actores); Requiere alineación de agendas empresariales con prioridades de recicladores; Tiempos de maduración de proyectos pueden ser largos; No hay convocatorias públicas abiertas (opera por identificación de oportunidades y articulación directa)</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Contactar a Fundación Avina y Latitud R para explorar alianza estratégica con Visión Circular ANDI. Presentar el modelo de trabajo de Visión Circular (articulación empresas-gremios-recicladores-gobierno) como complementario a Latitud R. Identificar líneas de co-inversión en proyectos de reciclaje inclusivo en Colombia que fortalezcan cadenas de valor de envases/empaques.</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Solicitar reunión con equipo de Latitud R y Fundación Avina (contacto vía latitudr.org o fundacionavina.net). Mapear empresas miembros de ANDI que ya participan en Latitud R para apalancar entrada. Preparar propuesta de valor de Visión Circular para alianza estratégica regional.</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Coordinación de alianzas estratégicas y proyectos de inclusión social / economía circular de Visión Circular</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Latitud R no es una convocatoria tradicional sino una plataforma de colaboración permanente. La información de redes sociales (Instagram, Facebook) de 2026 muestra actividad continua en Brasil, México y Perú. No hay evidencia explícita de proyectos activos en Colombia en las fuentes, pero la plataforma es regional y Colombia es país elegible. Se infiere posibilidad de articulación dado que empresas socias de Latitud R (Coca-Cola, PepsiCo, Nestlé) operan en Colombia y son parte del ecosistema ANDI.</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>1906d2cc84548674</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>

--- a/funding-agent/data/oportunidades_atraccion_recursos_vision_circular.xlsx
+++ b/funding-agent/data/oportunidades_atraccion_recursos_vision_circular.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI84"/>
+  <dimension ref="A1:AI86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15279,6 +15279,360 @@
         </is>
       </c>
       <c r="AI84" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VC-0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Financing Circular Economy - GIZ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GIZ</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Cooperación bilateral</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Colombia, América Latina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Financiación de proyectos de economía circular</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Grant no reembolsable; Asistencia técnica</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>https://www.giz.de/en/downloads/giz2022-en-financing-circula-economy-colombia.pdf</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>GIZ ofrece financiación y asistencia técnica para proyectos de economía circular en Colombia y América Latina. El objetivo es apoyar la implementación de la estrategia de economía circular en el país.</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>La oportunidad se alinea con los objetivos de Visión Circular ANDI, ya que busca apoyar la implementación de la estrategia de economía circular en Colombia.</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Proyectos de economía circular, financiación de proyectos de reciclaje y reducción de residuos</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Empresas, gremios, universidades, centros tecnológicos</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Investigar más a fondo la oportunidad y contactar a GIZ para obtener más información</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Contactar a GIZ para obtener más información</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>La oportunidad parece ser relevante para Visión Circular ANDI, pero es necesario obtener más información para determinar la elegibilidad y los requisitos específicos.</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>b7027534a5021fdf</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VC-0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Circulate Capital</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Circulate Capital</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Fondo de inversión</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>América Latina, incluyendo Colombia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Economía circular</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Financiación de proyectos de economía circular</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Inversión; Financiamiento concesional</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2 a 30 millones de USD</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Requiere verificación manual</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Requiere verificación</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>https://www.circulatecapital.com/apply-for-funding</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Circulate Capital ofrece financiación para proyectos de economía circular en América Latina, incluyendo Colombia. El objetivo es apoyar la implementación de la estrategia de economía circular en la región.</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>La oportunidad se alinea con los objetivos de Visión Circular ANDI, ya que busca apoyar la implementación de la estrategia de economía circular en Colombia.</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Proyectos de economía circular, financiación de proyectos de reciclaje y reducción de residuos</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Empresas, gremios, universidades, centros tecnológicos</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Investigar más a fondo la oportunidad y contactar a Circulate Capital para obtener más información</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Contactar a Circulate Capital para obtener más información</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Coordinación de proyectos</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>La oportunidad parece ser relevante para Visión Circular ANDI, pero es necesario obtener más información para determinar la elegibilidad y los requisitos específicos.</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>c64ba492eb8f4d27</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
